--- a/public/exports/29189560.xlsx
+++ b/public/exports/29189560.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027988</t>
+          <t xml:space="preserve">200027989</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">

--- a/public/exports/29189560.xlsx
+++ b/public/exports/29189560.xlsx
@@ -8914,7 +8914,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027989</t>
+          <t xml:space="preserve">200027988</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13339,7 +13339,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13564,7 +13564,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13639,7 +13639,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251069</t>
+          <t xml:space="preserve">311251072</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">

--- a/public/exports/29189560.xlsx
+++ b/public/exports/29189560.xlsx
@@ -13264,7 +13264,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13339,7 +13339,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13564,7 +13564,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13639,7 +13639,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251072</t>
+          <t xml:space="preserve">311251069</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
